--- a/L2-Step1-MOR-硬伤清单_10-28-2026.xlsx
+++ b/L2-Step1-MOR-硬伤清单_10-28-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOR 硬伤" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOR 硬伤'!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOR 硬伤'!$A$1:$F$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>★上下限仍是占位符 “X oC”。按 3.20 等应为 15–25 °C。</t>
+          <t>★上下限仍是占位符 “X oC”，应按 15–25 °C。紧接着的超温预警是 22–28 °C，本步控温却是 20±5 °C：目标 20 °C 已经低于预警低限，正常加料会一直报警，高限 28 °C 又高于 NOR 上限 25 °C。3.20.7、3.23.7、3.26.7 等同类 DIC 步的预警是 17–23 °C。这里改为 17–23 °C。</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>预警写成 低限 22 °C、高限 23 °C，低限比目标 20 °C 还高，加料过程会一直报警。其他氨基酸为 17–23 °C。改为 17–23 °C。</t>
+          <t>预警写成 低限 22 °C、高限 23 °C，低限比目标 20 °C 还高，加料过程会一直报警。3.20.7 等同类步骤为 17–23 °C（3.17.7 是另一套 22–28 °C，见该行）。改为 17–23 °C。</t>
         </is>
       </c>
     </row>
@@ -1507,17 +1507,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3.28（Leu16 前脱保护）第二次再溶胀</t>
+          <t>3.7.6 Phe23；3.10.5、3.18.5 的不合格处置</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>3.25.8 DMF addition</t>
+          <t>NMT 841 min</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>3.28 节里这一步编号写成 3.25.8，应为 3.28.8（全文两处，3.28 节那处错）。</t>
+          <t>Phe23 的偶联上限中英文都写 841 min，其余氨基酸写 840 min。3.10.5（NMeAsn22）、3.18.5（Ser20）本步上限是 840 min，不合格后继续取样的处置句仍写 841 min，处置比本步上限多 1 min。Phe23 改为 840 min；两处处置句改成与本步上限相同。</t>
         </is>
       </c>
     </row>
@@ -1537,17 +1537,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.13 Asn21；3.43；3.2.5</t>
+          <t>3.22.8 与 3.22.9</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>documented in Ins3.43.2</t>
+          <t>3.22.9 Resin reswelling wash 2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>交叉引用中英不一致：3.13 英文 “Ins3.13.5”、中文“3.13.7”；3.43 一处英文 3.43.2、中文 3.42.2；3.2.5 一处英文 3.1.3、中文 3.2.1。核对后统一。</t>
+          <t>3.22.8 已经是“溶胀后洗涤2”（加 12 V DMF）。3.22.9 不再加液，只鼓氮气、搅拌、排液，标题仍写洗涤2。批记录里同一次洗涤会出现两个“洗涤2”。3.22.9 改成该步的排液记录，或并入 3.22.8。</t>
         </is>
       </c>
     </row>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>版本说明 第 3 条</t>
+          <t>3.44 树脂洗涤</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>20±10 min (target: 10 min)</t>
+          <t>3.44.1 Sample</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>版本说明写封端 DIPEA 参考加料时间目标 10 min，3.4.3 正文写 20 ± 10 min（目标 20 min）。</t>
+          <t>3.44.1 用了两次：前面是脱保护后 IPAc 洗涤，这里是第 2 次洗涤的氯冉酸取样。两个操作不能共用一个指令号。取样改为 3.44.2。（3.43.5 同样把洗涤和 IPC 编成同一个号。）</t>
         </is>
       </c>
     </row>
@@ -1597,17 +1597,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.17.8、3.26.8 活化</t>
+          <t>3.28（Leu16 前脱保护）第二次再溶胀</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Maintain for NLT 15 min</t>
+          <t>3.25.8 DMF addition</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>英文 NLT 15 min（目标 20 min），中文 20 ± 5 min；参数表 NOR 15–25 min。中文优先，英文改为 20 ± 5 min。</t>
+          <t>3.28 节里这一步编号写成 3.25.8，应为 3.28.8（全文两处，3.28 节那处错）。</t>
         </is>
       </c>
     </row>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3.0 预处理</t>
+          <t>3.13 Asn21；3.43；3.2.5</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>搅拌5 min±5 min</t>
+          <t>documented in Ins3.43.2</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>英文 5 ± 2 min，中文 5 ± 5 min。</t>
+          <t>交叉引用中英不一致：3.13 英文 “Ins3.13.5”、中文“3.13.7”；3.43 一处英文 3.43.2、中文 3.42.2；3.2.5 一处英文 3.1.3、中文 3.2.1。核对后统一。</t>
         </is>
       </c>
     </row>
@@ -1657,17 +1657,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3.16、3.19、3.25 等脱保护后洗涤</t>
+          <t>版本说明 第 3 条</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>搅拌5±2 min（目标时间：10 min）</t>
+          <t>20±10 min (target: 10 min)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>中文 ±2 min 配目标 10 min；英文同时写 “Stir for 5±2 min … After stirring for 5±2 min”，搅拌写了两遍。3.4 封端后洗涤也有英文 5 ± 2 min、中文 10 ± 2 min 的不一致。</t>
+          <t>版本说明写封端 DIPEA 参考加料时间目标 10 min，3.4.3 正文写 20 ± 10 min（目标 20 min）。</t>
         </is>
       </c>
     </row>
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.5 等哌啶溶液确认</t>
+          <t>3.17.8、3.26.8 活化</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>17.50%~22.50%</t>
+          <t>Maintain for NLT 15 min</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>浓度 NOR 17.50–22.50% 和温度 NOR 只写在中文，英文句没有数字。参数表和 PVP 也没有浓度 NOR。</t>
+          <t>英文 NLT 15 min（目标 20 min），中文 20 ± 5 min；参数表 NOR 15–25 min。中文优先，英文改为 20 ± 5 min。</t>
         </is>
       </c>
     </row>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3.17.1、3.20.1 等</t>
+          <t>3.0 预处理</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>95±5 rpm</t>
+          <t>搅拌5 min±5 min</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>其余活化罐搅拌都是 95 ± 10 rpm。</t>
+          <t>英文 5 ± 2 min，中文 5 ± 5 min。</t>
         </is>
       </c>
     </row>
@@ -1742,22 +1742,22 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>原料信息表 3.37.1、3.37.5、3.38.1</t>
+          <t>3.16、3.19、3.25 等脱保护后洗涤</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>3.37.1</t>
+          <t>搅拌5±2 min（目标时间：10 min）</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>体积比（8、10、5）错填到“摩尔比”列。</t>
+          <t>中文 ±2 min 配目标 10 min；英文同时写 “Stir for 5±2 min … After stirring for 5±2 min”，搅拌写了两遍。3.4 封端后洗涤也有英文 5 ± 2 min、中文 10 ± 2 min 的不一致。</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>原料信息表 3.2.4 与 3.4.3</t>
+          <t>3.5 等哌啶溶液确认</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>129.24</t>
+          <t>17.50%~22.50%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>DIPEA 分子量写 129.25 和 129.24 两个值。</t>
+          <t>浓度 NOR 17.50–22.50% 和温度 NOR 只写在中文，英文句没有数字。参数表和 PVP 也没有浓度 NOR。</t>
         </is>
       </c>
     </row>
@@ -1797,27 +1797,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中英翻译</t>
+          <t>内部数值/逻辑</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>全文（约 300 处）</t>
+          <t>3.17.1、3.20.1 等</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>用于工艺性能执行</t>
+          <t>95±5 rpm</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>“确认”被成批替换成“执行”，且 MOR 规定中文为准：如“工艺性能执行”（应为工艺性能确认，即 PPQ）、“执行物料在复检日期”、“操作人员须执行反应体系温度…”、“拉曼扫描执行”、“各类执行”、“设备执行和配方执行”、“执行合计净重在投料范围内”。全文把这类“执行”改回“确认”，“执行人及日期”除外。</t>
+          <t>其余活化罐搅拌都是 95 ± 10 rpm。</t>
         </is>
       </c>
     </row>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>中英翻译</t>
+          <t>内部数值/逻辑</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3.5.3、3.8.3、3.11.3</t>
+          <t>原料信息表 3.37.1、3.37.5、3.38.1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>滤除至基本</t>
+          <t>3.37.1</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>中文“滤除至基本通过隔膜泵从合成釜中排出溶液”断句错乱；英文 “Filter until nearly no liquid outflow” 与后一句 Drain 重复。删去该半句。</t>
+          <t>体积比（8、10、5）错填到“摩尔比”列。</t>
         </is>
       </c>
     </row>
@@ -1857,27 +1857,27 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中英翻译</t>
+          <t>内部数值/逻辑</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>收料 Ins.4</t>
+          <t>原料信息表 3.2.4 与 3.4.3</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Particulate Drain</t>
+          <t>129.24</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>颗粒物滤棉译成 Particulate Drain，应为 particulate filter（分装节已写对）。</t>
+          <t>DIPEA 分子量写 129.25 和 129.24 两个值。</t>
         </is>
       </c>
     </row>
@@ -1892,22 +1892,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>收料 Ins.4 转移</t>
+          <t>全文（约 300 处）</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>use a cabinet when transferring</t>
+          <t>用于工艺性能执行</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>中文“保温箱”，英文 cabinet。2–8 °C 转移应为 insulated box / cool box。</t>
+          <t>“确认”被成批替换成“执行”，且 MOR 规定中文为准：如“工艺性能执行”（应为工艺性能确认，即 PPQ）、“执行物料在复检日期”、“操作人员须执行反应体系温度…”、“拉曼扫描执行”、“各类执行”、“设备执行和配方执行”、“执行合计净重在投料范围内”。全文把这类“执行”改回“确认”，“执行人及日期”除外。</t>
         </is>
       </c>
     </row>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>英文缩写表</t>
+          <t>3.5.3、3.8.3、3.11.3</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>滤除至基本</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Qty 的中文写“质量”，应为“数量”；缩写表缺 CPP、NOR、PAR、DMF、DIC、DIPEA、IPAc、MTBE、LDPE、HDPE、OEB、FIO 等正文实际用到的缩写，却列了没用到的 MP、BP。</t>
+          <t>中文“滤除至基本通过隔膜泵从合成釜中排出溶液”断句错乱；英文 “Filter until nearly no liquid outflow” 与后一句 Drain 重复。删去该半句。</t>
         </is>
       </c>
     </row>
@@ -1952,22 +1952,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.18、3.21、3.24、3.27 取样</t>
+          <t>收料 Ins.4</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Kaiser test record</t>
+          <t>Particulate Drain</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>其余偶联写 ninhydrin test record，这四处写 Kaiser test record，记录名统一。</t>
+          <t>颗粒物滤棉译成 Particulate Drain，应为 particulate filter（分装节已写对）。</t>
         </is>
       </c>
     </row>
@@ -1977,27 +1977,27 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>笔误/格式</t>
+          <t>中英翻译</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>多处</t>
+          <t>收料 Ins.4 转移</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Shirnk</t>
+          <t>use a cabinet when transferring</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Shirnk（2 处）、soulution（3）、diaphragmgm（2）、Ddeprotection、Adust、activation tan、Pyriine（代码表）、hastelly、cleacing、Ckecked、Checeked、Checkmed（3）、Ttransfer、additon、Sloid、LDPEpowder、butunpack（2）、solutionand、drainingdiaphragm、“conten t”、“Solid-peptide peptide synthesizer”、“哈式合金”、3.46 中文标题前多一个“芴”、TJ4S-1213-Sy15-RT01。</t>
+          <t>中文“保温箱”，英文 cabinet。2–8 °C 转移应为 insulated box / cool box。</t>
         </is>
       </c>
     </row>
@@ -2007,27 +2007,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>笔误/格式</t>
+          <t>中英翻译</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>分装各节</t>
+          <t>3.5.9、3.11.9、3.31.9</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Page 32~62 of 624</t>
+          <t>3.5.9 Resin reswelling wash 1</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>文件共 674 页（30 处）。改页码或去掉总页数。</t>
+          <t>英文写 wash 1，中文写“洗涤2”（3.11.9 少一个“后”）。对照同结构的 3.8.9，英文是 wash 2、中文是洗涤2，前一步是加 DMF。MOR 以中文为准，这三处英文改为 wash 2；3.11.9 中文改为“溶胀后洗涤2”。</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>笔误/格式</t>
+          <t>中英翻译</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2047,17 +2047,17 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3.40.3；3.45；目录 3.8、3.25</t>
+          <t>英文缩写表</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Deprotection of Fmoc-L-Leu-OH activation</t>
+          <t>Qty</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>标题与内容不符：3.40.3 写“Leu 活化的脱保护”；3.45 只有再溶胀却叫 “(14) Deprotection”；目录 3.8、3.25 把脱保护标成下一个氨基酸名。3.43.5 编号用了两次。</t>
+          <t>Qty 的中文写“质量”，应为“数量”；缩写表缺 CPP、NOR、PAR、DMF、DIC、DIPEA、IPAc、MTBE、LDPE、HDPE、OEB、FIO 等正文实际用到的缩写，却列了没用到的 MP、BP。</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>笔误/格式</t>
+          <t>中英翻译</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3.10.5</t>
+          <t>3.18、3.21、3.24、3.27 取样</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>(target: 4 h) (target：4 h)</t>
+          <t>Kaiser test record</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>目标重复写了两次。</t>
+          <t>其余偶联写 ninhydrin test record，这四处写 Kaiser test record，记录名统一。</t>
         </is>
       </c>
     </row>
@@ -2107,17 +2107,17 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>多处</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>(target: 5 ℃.</t>
+          <t>Shirnk</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>括号没关。</t>
+          <t>Shirnk（2 处）、soulution（3）、diaphragmgm（2）、Ddeprotection、Adust、activation tan、Pyriine（代码表）、hastelly、cleacing、Ckecked、Checeked、Checkmed（3）、Ttransfer、additon、Sloid、LDPEpowder、butunpack（2）、solutionand、drainingdiaphragm、“conten t”、“Solid-peptide peptide synthesizer”、“哈式合金”、3.46 中文标题前多一个“芴”、TJ4S-1213-Sy15-RT01。</t>
         </is>
       </c>
     </row>
@@ -2137,17 +2137,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3.15.6</t>
+          <t>分装各节</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Charge 364.03 kg DMF addition</t>
+          <t>Page 32~62 of 624</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>英文语法不通，且缺称量范围（中文有）。</t>
+          <t>文件共 674 页（30 处）。改页码或去掉总页数。</t>
         </is>
       </c>
     </row>
@@ -2167,22 +2167,142 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
+          <t>3.40.3；3.45；目录 3.8、3.25</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Deprotection of Fmoc-L-Leu-OH activation</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>标题与内容不符：3.40.3 写“Leu 活化的脱保护”；3.45 只有再溶胀却叫 “(14) Deprotection”；目录 3.8、3.25 把脱保护标成下一个氨基酸名。3.43.5 编号用了两次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>笔误/格式</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>3.10.5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>(target: 4 h) (target：4 h)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>目标重复写了两次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>笔误/格式</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>3.6.5</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>(target: 5 ℃.</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>括号没关。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>笔误/格式</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>3.15.6</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Charge 364.03 kg DMF addition</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>英文语法不通，且缺称量范围（中文有）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>笔误/格式</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
           <t>过程中间体信息</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>÷ 1000 kg/mol]</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>公式多一个 “]”。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F57"/>
+  <autoFilter ref="A1:F61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
